--- a/Team-Data/2012-13/1-6-2012-13.xlsx
+++ b/Team-Data/2012-13/1-6-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,10 +806,10 @@
         <v>1.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF2" t="n">
         <v>8</v>
@@ -751,7 +818,7 @@
         <v>8</v>
       </c>
       <c r="AH2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI2" t="n">
         <v>12</v>
@@ -790,7 +857,7 @@
         <v>25</v>
       </c>
       <c r="AU2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV2" t="n">
         <v>13</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-1.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE3" t="n">
         <v>16</v>
@@ -951,7 +1018,7 @@
         <v>28</v>
       </c>
       <c r="AN3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO3" t="n">
         <v>20</v>
@@ -972,7 +1039,7 @@
         <v>30</v>
       </c>
       <c r="AU3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV3" t="n">
         <v>10</v>
@@ -984,7 +1051,7 @@
         <v>28</v>
       </c>
       <c r="AY3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ3" t="n">
         <v>24</v>
@@ -996,7 +1063,7 @@
         <v>21</v>
       </c>
       <c r="BC3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
@@ -1103,10 +1170,10 @@
         <v>0.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF4" t="n">
         <v>12</v>
@@ -1115,16 +1182,16 @@
         <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ4" t="n">
         <v>28</v>
       </c>
       <c r="AK4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL4" t="n">
         <v>12</v>
@@ -1148,7 +1215,7 @@
         <v>10</v>
       </c>
       <c r="AS4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT4" t="n">
         <v>19</v>
@@ -1172,10 +1239,10 @@
         <v>4</v>
       </c>
       <c r="BA4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC4" t="n">
         <v>14</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
@@ -1207,85 +1274,85 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="n">
         <v>24</v>
       </c>
       <c r="G5" t="n">
-        <v>0.273</v>
+        <v>0.25</v>
       </c>
       <c r="H5" t="n">
-        <v>48.8</v>
+        <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="J5" t="n">
-        <v>83.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K5" t="n">
         <v>0.423</v>
       </c>
       <c r="L5" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="M5" t="n">
-        <v>17.5</v>
+        <v>17.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.345</v>
+        <v>0.348</v>
       </c>
       <c r="O5" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="R5" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="S5" t="n">
+        <v>30</v>
+      </c>
+      <c r="T5" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="U5" t="n">
         <v>19.6</v>
       </c>
-      <c r="P5" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="R5" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="T5" t="n">
-        <v>42</v>
-      </c>
-      <c r="U5" t="n">
-        <v>19.4</v>
-      </c>
       <c r="V5" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W5" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="X5" t="n">
         <v>6.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="Z5" t="n">
         <v>19.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>96.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>-7.7</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AE5" t="n">
         <v>27</v>
@@ -1297,25 +1364,25 @@
         <v>27</v>
       </c>
       <c r="AH5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI5" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AJ5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK5" t="n">
         <v>27</v>
       </c>
       <c r="AL5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM5" t="n">
         <v>25</v>
       </c>
       <c r="AN5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AO5" t="n">
         <v>4</v>
@@ -1324,28 +1391,28 @@
         <v>3</v>
       </c>
       <c r="AQ5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AR5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AS5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AV5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AX5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY5" t="n">
         <v>30</v>
@@ -1354,13 +1421,13 @@
         <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BB5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BC5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>1</v>
       </c>
       <c r="AD6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1482,13 +1549,13 @@
         <v>27</v>
       </c>
       <c r="AI6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ6" t="n">
         <v>25</v>
       </c>
       <c r="AK6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL6" t="n">
         <v>30</v>
@@ -1497,7 +1564,7 @@
         <v>30</v>
       </c>
       <c r="AN6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO6" t="n">
         <v>8</v>
@@ -1509,10 +1576,10 @@
         <v>3</v>
       </c>
       <c r="AR6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
@@ -1649,10 +1716,10 @@
         <v>-5.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF7" t="n">
         <v>29</v>
@@ -1667,7 +1734,7 @@
         <v>24</v>
       </c>
       <c r="AJ7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK7" t="n">
         <v>29</v>
@@ -1700,13 +1767,13 @@
         <v>15</v>
       </c>
       <c r="AU7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AV7" t="n">
         <v>21</v>
       </c>
       <c r="AW7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX7" t="n">
         <v>30</v>
@@ -1718,7 +1785,7 @@
         <v>29</v>
       </c>
       <c r="BA7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB7" t="n">
         <v>23</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>-4.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE8" t="n">
         <v>21</v>
@@ -1867,7 +1934,7 @@
         <v>19</v>
       </c>
       <c r="AP8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ8" t="n">
         <v>7</v>
@@ -1900,7 +1967,7 @@
         <v>26</v>
       </c>
       <c r="BA8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
@@ -1935,70 +2002,70 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F9" t="n">
         <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>0.556</v>
+        <v>0.543</v>
       </c>
       <c r="H9" t="n">
         <v>48.3</v>
       </c>
       <c r="I9" t="n">
-        <v>39.4</v>
+        <v>39.3</v>
       </c>
       <c r="J9" t="n">
-        <v>84.59999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="K9" t="n">
-        <v>0.465</v>
+        <v>0.466</v>
       </c>
       <c r="L9" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="M9" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="N9" t="n">
-        <v>0.33</v>
+        <v>0.329</v>
       </c>
       <c r="O9" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="P9" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.679</v>
+        <v>0.68</v>
       </c>
       <c r="R9" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="S9" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="T9" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
       <c r="U9" t="n">
-        <v>23.4</v>
+        <v>23.1</v>
       </c>
       <c r="V9" t="n">
-        <v>15.3</v>
+        <v>15.5</v>
       </c>
       <c r="W9" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="X9" t="n">
         <v>6.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="Z9" t="n">
         <v>20.6</v>
@@ -2007,40 +2074,40 @@
         <v>21.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>102</v>
+        <v>101.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AF9" t="n">
         <v>15</v>
       </c>
       <c r="AG9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI9" t="n">
         <v>2</v>
       </c>
       <c r="AJ9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK9" t="n">
         <v>5</v>
       </c>
       <c r="AL9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AM9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN9" t="n">
         <v>28</v>
@@ -2055,37 +2122,37 @@
         <v>30</v>
       </c>
       <c r="AR9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT9" t="n">
         <v>2</v>
       </c>
       <c r="AU9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV9" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AW9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX9" t="n">
         <v>4</v>
       </c>
       <c r="AY9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ9" t="n">
         <v>21</v>
       </c>
       <c r="BA9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC9" t="n">
         <v>8</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
@@ -2117,46 +2184,46 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E10" t="n">
         <v>13</v>
       </c>
       <c r="F10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G10" t="n">
-        <v>0.361</v>
+        <v>0.371</v>
       </c>
       <c r="H10" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="I10" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J10" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.443</v>
+        <v>0.441</v>
       </c>
       <c r="L10" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M10" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0.374</v>
+        <v>0.377</v>
       </c>
       <c r="O10" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="P10" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.717</v>
+        <v>0.718</v>
       </c>
       <c r="R10" t="n">
         <v>12.6</v>
@@ -2171,31 +2238,31 @@
         <v>20.1</v>
       </c>
       <c r="V10" t="n">
-        <v>15.3</v>
+        <v>15.1</v>
       </c>
       <c r="W10" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="X10" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y10" t="n">
         <v>5.7</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="AA10" t="n">
         <v>20.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>95</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.6</v>
+        <v>-1.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="n">
         <v>21</v>
@@ -2204,10 +2271,10 @@
         <v>25</v>
       </c>
       <c r="AG10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AI10" t="n">
         <v>21</v>
@@ -2216,7 +2283,7 @@
         <v>21</v>
       </c>
       <c r="AK10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AL10" t="n">
         <v>21</v>
@@ -2228,7 +2295,7 @@
         <v>8</v>
       </c>
       <c r="AO10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP10" t="n">
         <v>10</v>
@@ -2240,28 +2307,28 @@
         <v>8</v>
       </c>
       <c r="AS10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU10" t="n">
         <v>26</v>
       </c>
       <c r="AV10" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AW10" t="n">
         <v>29</v>
       </c>
       <c r="AX10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AY10" t="n">
         <v>21</v>
       </c>
       <c r="AZ10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA10" t="n">
         <v>10</v>
@@ -2270,7 +2337,7 @@
         <v>22</v>
       </c>
       <c r="BC10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
@@ -2377,22 +2444,22 @@
         <v>2.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF11" t="n">
         <v>7</v>
       </c>
       <c r="AG11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI11" t="n">
         <v>7</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>6</v>
       </c>
       <c r="AJ11" t="n">
         <v>8</v>
@@ -2452,7 +2519,7 @@
         <v>9</v>
       </c>
       <c r="BC11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
@@ -2559,10 +2626,10 @@
         <v>2.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
@@ -2741,10 +2808,10 @@
         <v>1.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF13" t="n">
         <v>10</v>
@@ -2756,7 +2823,7 @@
         <v>15</v>
       </c>
       <c r="AI13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AJ13" t="n">
         <v>24</v>
@@ -2768,16 +2835,16 @@
         <v>19</v>
       </c>
       <c r="AM13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AN13" t="n">
         <v>25</v>
       </c>
       <c r="AO13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ13" t="n">
         <v>24</v>
@@ -2795,7 +2862,7 @@
         <v>28</v>
       </c>
       <c r="AV13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW13" t="n">
         <v>27</v>
@@ -2810,7 +2877,7 @@
         <v>12</v>
       </c>
       <c r="BA13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB13" t="n">
         <v>29</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2953,7 +3020,7 @@
         <v>11</v>
       </c>
       <c r="AN14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO14" t="n">
         <v>11</v>
@@ -2995,7 +3062,7 @@
         <v>3</v>
       </c>
       <c r="BB14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC14" t="n">
         <v>2</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
@@ -3027,22 +3094,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E15" t="n">
         <v>15</v>
       </c>
       <c r="F15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G15" t="n">
-        <v>0.455</v>
+        <v>0.469</v>
       </c>
       <c r="H15" t="n">
         <v>48.2</v>
       </c>
       <c r="I15" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J15" t="n">
         <v>81.09999999999999</v>
@@ -3054,16 +3121,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="O15" t="n">
         <v>20.6</v>
       </c>
       <c r="P15" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="Q15" t="n">
         <v>0.6899999999999999</v>
@@ -3078,40 +3145,40 @@
         <v>45.8</v>
       </c>
       <c r="U15" t="n">
-        <v>21.5</v>
+        <v>21.2</v>
       </c>
       <c r="V15" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W15" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X15" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z15" t="n">
         <v>19.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.9</v>
+        <v>102.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AE15" t="n">
         <v>18</v>
       </c>
       <c r="AF15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG15" t="n">
         <v>19</v>
@@ -3120,7 +3187,7 @@
         <v>28</v>
       </c>
       <c r="AI15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ15" t="n">
         <v>22</v>
@@ -3150,7 +3217,7 @@
         <v>5</v>
       </c>
       <c r="AS15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT15" t="n">
         <v>4</v>
@@ -3159,16 +3226,16 @@
         <v>19</v>
       </c>
       <c r="AV15" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AW15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AX15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ15" t="n">
         <v>14</v>
@@ -3180,7 +3247,7 @@
         <v>5</v>
       </c>
       <c r="BC15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
@@ -3209,37 +3276,37 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F16" t="n">
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>0.677</v>
+        <v>0.667</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J16" t="n">
-        <v>82.5</v>
+        <v>83</v>
       </c>
       <c r="K16" t="n">
-        <v>0.437</v>
+        <v>0.434</v>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="M16" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0.35</v>
+        <v>0.352</v>
       </c>
       <c r="O16" t="n">
         <v>17.1</v>
@@ -3251,10 +3318,10 @@
         <v>0.802</v>
       </c>
       <c r="R16" t="n">
-        <v>13.4</v>
+        <v>13.6</v>
       </c>
       <c r="S16" t="n">
-        <v>29.7</v>
+        <v>29.5</v>
       </c>
       <c r="T16" t="n">
         <v>43.1</v>
@@ -3263,10 +3330,10 @@
         <v>20.7</v>
       </c>
       <c r="V16" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="W16" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="X16" t="n">
         <v>5.5</v>
@@ -3281,13 +3348,13 @@
         <v>20</v>
       </c>
       <c r="AB16" t="n">
-        <v>94.2</v>
+        <v>94.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE16" t="n">
         <v>7</v>
@@ -3305,10 +3372,10 @@
         <v>20</v>
       </c>
       <c r="AJ16" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AK16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL16" t="n">
         <v>29</v>
@@ -3323,7 +3390,7 @@
         <v>13</v>
       </c>
       <c r="AP16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AQ16" t="n">
         <v>2</v>
@@ -3332,37 +3399,37 @@
         <v>3</v>
       </c>
       <c r="AS16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT16" t="n">
         <v>13</v>
       </c>
       <c r="AU16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AW16" t="n">
         <v>2</v>
       </c>
       <c r="AX16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY16" t="n">
         <v>22</v>
       </c>
       <c r="AZ16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB16" t="n">
         <v>24</v>
       </c>
       <c r="BC16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F17" t="n">
         <v>9</v>
       </c>
       <c r="G17" t="n">
-        <v>0.719</v>
+        <v>0.71</v>
       </c>
       <c r="H17" t="n">
         <v>48.5</v>
@@ -3409,10 +3476,10 @@
         <v>38.4</v>
       </c>
       <c r="J17" t="n">
-        <v>78.3</v>
+        <v>78.2</v>
       </c>
       <c r="K17" t="n">
-        <v>0.49</v>
+        <v>0.491</v>
       </c>
       <c r="L17" t="n">
         <v>8.5</v>
@@ -3421,58 +3488,58 @@
         <v>21.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0.393</v>
+        <v>0.394</v>
       </c>
       <c r="O17" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="P17" t="n">
-        <v>23</v>
+        <v>23.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.768</v>
+        <v>0.764</v>
       </c>
       <c r="R17" t="n">
         <v>8</v>
       </c>
       <c r="S17" t="n">
-        <v>31</v>
+        <v>30.7</v>
       </c>
       <c r="T17" t="n">
-        <v>39.1</v>
+        <v>38.7</v>
       </c>
       <c r="U17" t="n">
         <v>22.3</v>
       </c>
       <c r="V17" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W17" t="n">
         <v>8.1</v>
       </c>
       <c r="X17" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>103</v>
+        <v>103.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF17" t="n">
         <v>3</v>
@@ -3487,7 +3554,7 @@
         <v>4</v>
       </c>
       <c r="AJ17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK17" t="n">
         <v>1</v>
@@ -3505,10 +3572,10 @@
         <v>9</v>
       </c>
       <c r="AP17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3526,10 +3593,10 @@
         <v>5</v>
       </c>
       <c r="AW17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX17" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3538,13 +3605,13 @@
         <v>6</v>
       </c>
       <c r="BA17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BB17" t="n">
         <v>4</v>
       </c>
       <c r="BC17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-1.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
@@ -3690,7 +3757,7 @@
         <v>18</v>
       </c>
       <c r="AQ18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR18" t="n">
         <v>9</v>
@@ -3702,7 +3769,7 @@
         <v>12</v>
       </c>
       <c r="AU18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV18" t="n">
         <v>12</v>
@@ -3723,7 +3790,7 @@
         <v>15</v>
       </c>
       <c r="BB18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC18" t="n">
         <v>17</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>0.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE19" t="n">
         <v>18</v>
@@ -3851,7 +3918,7 @@
         <v>23</v>
       </c>
       <c r="AJ19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK19" t="n">
         <v>26</v>
@@ -3875,10 +3942,10 @@
         <v>23</v>
       </c>
       <c r="AR19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AT19" t="n">
         <v>1</v>
@@ -3893,7 +3960,7 @@
         <v>19</v>
       </c>
       <c r="AX19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY19" t="n">
         <v>23</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
@@ -4015,10 +4082,10 @@
         <v>-5.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF20" t="n">
         <v>28</v>
@@ -4027,10 +4094,10 @@
         <v>28</v>
       </c>
       <c r="AH20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ20" t="n">
         <v>26</v>
@@ -4042,7 +4109,7 @@
         <v>15</v>
       </c>
       <c r="AM20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN20" t="n">
         <v>6</v>
@@ -4054,13 +4121,13 @@
         <v>28</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR20" t="n">
         <v>20</v>
       </c>
       <c r="AS20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT20" t="n">
         <v>23</v>
@@ -4069,7 +4136,7 @@
         <v>20</v>
       </c>
       <c r="AV20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW20" t="n">
         <v>28</v>
@@ -4084,7 +4151,7 @@
         <v>16</v>
       </c>
       <c r="BA20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB20" t="n">
         <v>28</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>5.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE21" t="n">
         <v>4</v>
@@ -4209,7 +4276,7 @@
         <v>5</v>
       </c>
       <c r="AH21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI21" t="n">
         <v>8</v>
@@ -4239,13 +4306,13 @@
         <v>16</v>
       </c>
       <c r="AR21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU21" t="n">
         <v>25</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F22" t="n">
         <v>7</v>
       </c>
       <c r="G22" t="n">
-        <v>0.788</v>
+        <v>0.781</v>
       </c>
       <c r="H22" t="n">
         <v>48.5</v>
@@ -4328,28 +4395,28 @@
         <v>7.6</v>
       </c>
       <c r="M22" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="N22" t="n">
-        <v>0.401</v>
+        <v>0.406</v>
       </c>
       <c r="O22" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="P22" t="n">
-        <v>27</v>
+        <v>27.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.845</v>
+        <v>0.843</v>
       </c>
       <c r="R22" t="n">
         <v>10.4</v>
       </c>
       <c r="S22" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="T22" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="U22" t="n">
         <v>21.8</v>
@@ -4361,7 +4428,7 @@
         <v>8</v>
       </c>
       <c r="X22" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="Y22" t="n">
         <v>3.8</v>
@@ -4370,16 +4437,16 @@
         <v>20.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB22" t="n">
         <v>105.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -4397,7 +4464,7 @@
         <v>9</v>
       </c>
       <c r="AJ22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK22" t="n">
         <v>3</v>
@@ -4421,10 +4488,10 @@
         <v>1</v>
       </c>
       <c r="AR22" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AS22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT22" t="n">
         <v>9</v>
@@ -4436,7 +4503,7 @@
         <v>29</v>
       </c>
       <c r="AW22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-3</v>
       </c>
       <c r="AD23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE23" t="n">
         <v>24</v>
@@ -4570,7 +4637,7 @@
         <v>21</v>
       </c>
       <c r="AG23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH23" t="n">
         <v>21</v>
@@ -4615,7 +4682,7 @@
         <v>9</v>
       </c>
       <c r="AV23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-3.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE24" t="n">
         <v>18</v>
@@ -4758,7 +4825,7 @@
         <v>23</v>
       </c>
       <c r="AI24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ24" t="n">
         <v>5</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
@@ -4847,34 +4914,34 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E25" t="n">
         <v>12</v>
       </c>
       <c r="F25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G25" t="n">
-        <v>0.343</v>
+        <v>0.353</v>
       </c>
       <c r="H25" t="n">
         <v>48.4</v>
       </c>
       <c r="I25" t="n">
-        <v>37.9</v>
+        <v>38.1</v>
       </c>
       <c r="J25" t="n">
-        <v>84.7</v>
+        <v>84.8</v>
       </c>
       <c r="K25" t="n">
-        <v>0.448</v>
+        <v>0.45</v>
       </c>
       <c r="L25" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="M25" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="N25" t="n">
         <v>0.333</v>
@@ -4886,22 +4953,22 @@
         <v>19.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.749</v>
+        <v>0.748</v>
       </c>
       <c r="R25" t="n">
         <v>11.1</v>
       </c>
       <c r="S25" t="n">
-        <v>28.7</v>
+        <v>29</v>
       </c>
       <c r="T25" t="n">
-        <v>39.8</v>
+        <v>40</v>
       </c>
       <c r="U25" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="V25" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="W25" t="n">
         <v>8</v>
@@ -4910,7 +4977,7 @@
         <v>5.7</v>
       </c>
       <c r="Y25" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z25" t="n">
         <v>20.3</v>
@@ -4919,13 +4986,13 @@
         <v>18.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>96.3</v>
+        <v>96.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>-4.1</v>
+        <v>-3.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE25" t="n">
         <v>24</v>
@@ -4937,10 +5004,10 @@
         <v>26</v>
       </c>
       <c r="AH25" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ25" t="n">
         <v>2</v>
@@ -4949,10 +5016,10 @@
         <v>13</v>
       </c>
       <c r="AL25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AN25" t="n">
         <v>27</v>
@@ -4973,31 +5040,31 @@
         <v>29</v>
       </c>
       <c r="AT25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV25" t="n">
         <v>4</v>
       </c>
       <c r="AW25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY25" t="n">
         <v>14</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>12</v>
       </c>
       <c r="AZ25" t="n">
         <v>20</v>
       </c>
       <c r="BA25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC25" t="n">
         <v>24</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE26" t="n">
         <v>13</v>
@@ -5116,7 +5183,7 @@
         <v>12</v>
       </c>
       <c r="AG26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH26" t="n">
         <v>5</v>
@@ -5125,7 +5192,7 @@
         <v>19</v>
       </c>
       <c r="AJ26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK26" t="n">
         <v>21</v>
@@ -5146,13 +5213,13 @@
         <v>23</v>
       </c>
       <c r="AQ26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT26" t="n">
         <v>22</v>
@@ -5179,7 +5246,7 @@
         <v>25</v>
       </c>
       <c r="BB26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC26" t="n">
         <v>20</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-4.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE27" t="n">
         <v>21</v>
@@ -5328,10 +5395,10 @@
         <v>15</v>
       </c>
       <c r="AQ27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS27" t="n">
         <v>30</v>
@@ -5349,10 +5416,10 @@
         <v>9</v>
       </c>
       <c r="AX27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ27" t="n">
         <v>23</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5571,7 @@
         <v>3</v>
       </c>
       <c r="AO28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP28" t="n">
         <v>19</v>
@@ -5519,13 +5586,13 @@
         <v>2</v>
       </c>
       <c r="AT28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW28" t="n">
         <v>6</v>
@@ -5534,7 +5601,7 @@
         <v>16</v>
       </c>
       <c r="AY28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ28" t="n">
         <v>2</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
@@ -5575,25 +5642,25 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E29" t="n">
         <v>12</v>
       </c>
       <c r="F29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G29" t="n">
-        <v>0.353</v>
+        <v>0.364</v>
       </c>
       <c r="H29" t="n">
         <v>48.9</v>
       </c>
       <c r="I29" t="n">
-        <v>35.6</v>
+        <v>35.7</v>
       </c>
       <c r="J29" t="n">
-        <v>81.8</v>
+        <v>82</v>
       </c>
       <c r="K29" t="n">
         <v>0.435</v>
@@ -5614,22 +5681,22 @@
         <v>22.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.773</v>
+        <v>0.774</v>
       </c>
       <c r="R29" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S29" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="T29" t="n">
-        <v>39.6</v>
+        <v>39.8</v>
       </c>
       <c r="U29" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="V29" t="n">
-        <v>12.7</v>
+        <v>12.5</v>
       </c>
       <c r="W29" t="n">
         <v>7.5</v>
@@ -5641,31 +5708,31 @@
         <v>5.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="AA29" t="n">
         <v>19.6</v>
       </c>
       <c r="AB29" t="n">
-        <v>96.7</v>
+        <v>96.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>-2.8</v>
+        <v>-2.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AE29" t="n">
         <v>24</v>
       </c>
       <c r="AF29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG29" t="n">
         <v>24</v>
       </c>
-      <c r="AG29" t="n">
-        <v>25</v>
-      </c>
       <c r="AH29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI29" t="n">
         <v>22</v>
@@ -5674,7 +5741,7 @@
         <v>19</v>
       </c>
       <c r="AK29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL29" t="n">
         <v>9</v>
@@ -5692,28 +5759,28 @@
         <v>13</v>
       </c>
       <c r="AQ29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS29" t="n">
         <v>25</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>27</v>
       </c>
       <c r="AT29" t="n">
         <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV29" t="n">
         <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY29" t="n">
         <v>18</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
@@ -5835,19 +5902,19 @@
         <v>-0.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="n">
         <v>15</v>
       </c>
       <c r="AF30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG30" t="n">
         <v>17</v>
       </c>
       <c r="AH30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI30" t="n">
         <v>18</v>
@@ -5856,7 +5923,7 @@
         <v>16</v>
       </c>
       <c r="AK30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL30" t="n">
         <v>20</v>
@@ -5874,7 +5941,7 @@
         <v>7</v>
       </c>
       <c r="AQ30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR30" t="n">
         <v>5</v>
@@ -5889,13 +5956,13 @@
         <v>10</v>
       </c>
       <c r="AV30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW30" t="n">
         <v>10</v>
       </c>
       <c r="AX30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY30" t="n">
         <v>24</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
@@ -5939,28 +6006,28 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E31" t="n">
         <v>4</v>
       </c>
       <c r="F31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G31" t="n">
-        <v>0.125</v>
+        <v>0.129</v>
       </c>
       <c r="H31" t="n">
         <v>49.1</v>
       </c>
       <c r="I31" t="n">
-        <v>33.9</v>
+        <v>34.1</v>
       </c>
       <c r="J31" t="n">
-        <v>83.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.407</v>
+        <v>0.409</v>
       </c>
       <c r="L31" t="n">
         <v>6.4</v>
@@ -5969,31 +6036,31 @@
         <v>20.1</v>
       </c>
       <c r="N31" t="n">
-        <v>0.317</v>
+        <v>0.318</v>
       </c>
       <c r="O31" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="P31" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.741</v>
+        <v>0.747</v>
       </c>
       <c r="R31" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S31" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="T31" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
       <c r="U31" t="n">
         <v>20.7</v>
       </c>
       <c r="V31" t="n">
-        <v>15.2</v>
+        <v>15.5</v>
       </c>
       <c r="W31" t="n">
         <v>7.5</v>
@@ -6002,28 +6069,28 @@
         <v>4.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="AB31" t="n">
-        <v>88.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>-8.300000000000001</v>
+        <v>-7.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AE31" t="n">
         <v>30</v>
       </c>
       <c r="AF31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG31" t="n">
         <v>30</v>
@@ -6032,7 +6099,7 @@
         <v>2</v>
       </c>
       <c r="AI31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ31" t="n">
         <v>11</v>
@@ -6056,43 +6123,43 @@
         <v>25</v>
       </c>
       <c r="AQ31" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AR31" t="n">
         <v>16</v>
       </c>
       <c r="AS31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV31" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AW31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY31" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ31" t="n">
         <v>22</v>
       </c>
       <c r="BA31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB31" t="n">
         <v>30</v>
       </c>
       <c r="BC31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-6-2012-13</t>
+          <t>2013-01-06</t>
         </is>
       </c>
     </row>
